--- a/光伏配储项目/电价数据/2026/烟墩站.xlsx
+++ b/光伏配储项目/电价数据/2026/烟墩站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5535800000000001</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.51345</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.8548600000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.12413</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.01527</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.91147</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.70989</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.7195199999999999</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.53474</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.58689</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.5203300000000001</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.68122</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.68136</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.67161</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.51362</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.69912</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.68937</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.6521</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.67775</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.52255</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.6921900000000001</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.54242</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.69024</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.69809</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.54692</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.72312</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.81267</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.40191</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.8568600000000001</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.6758999999999999</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.6711</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.30551</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.45141</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.73278</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.75547</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.00828</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.99254</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.08342</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.74997</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.69686</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.50081</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.40632</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.40366</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.40829</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.7831399999999999</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.9482999999999999</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.31081</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.52271</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.7587200000000001</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.42555</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.7666000000000001</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.74664</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.9266599999999999</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.89332</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.04665</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.3135</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.11965</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.11671</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.73346</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.20832</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.1678</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.09631</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.22746</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.5341</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.10108</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.24579</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.47519</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.30357</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.235</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.79796</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.40928</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.35293</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.28354</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.80272</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47923</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4105</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41268</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42189</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.16705</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.03666</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.17616</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53624</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5226499999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50627</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51242</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.61029</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.51044</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.58461</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.48927</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.48267</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.5174299999999999</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.49937</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.50968</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.5096499999999999</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.49937</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.50603</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.55472</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.76246</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.06606</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.83602</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.5879500000000001</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.48163</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.5345700000000001</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.45483</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.50636</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.9339</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.14976</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.77485</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.11925</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.03661</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.98534</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.70696</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.54755</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.5663400000000001</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.6788200000000001</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.1519</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.22957</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.47338</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.30526</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.15662</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.62745</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.07785</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.81686</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.24996</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.13451</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.28256</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.6214400000000001</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.63774</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.56985</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.6216799999999999</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.15885</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.16691</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.17561</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.17021</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.96696</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.18773</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.20253</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.19399</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.66858</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.15998</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20548</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.20831</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.50455</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.40922</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.16629</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.50957</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.26388</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.74258</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.76486</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.91538</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44058</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41311</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33341</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.60046</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.6801200000000001</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.6904199999999999</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.53084</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.57464</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.5054</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.8277899999999999</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.5905</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.5825199999999999</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.55137</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.55392</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.62919</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.48276</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.5780700000000001</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.48531</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.57262</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.5216900000000001</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.55379</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.4918</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.50875</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.4941</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.50431</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.45851</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.6921499999999999</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.8303200000000001</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.10739</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.87342</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.74387</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.70265</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.6042000000000001</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.6429600000000001</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.42512</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.7284299999999999</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.16346</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.52015</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.67615</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.1657</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.61894</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.18734</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.16365</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.7921</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.9381499999999999</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.16243</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.1639</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.8915</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.55932</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.41353</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.47453</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.67399</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.16448</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.02736</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.16303</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.39078</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.23385</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.1644</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.21534</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.20922</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.39936</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.26777</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.28478</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.64752</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.16956</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.17252</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.78116</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.03769</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.07729</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.09815</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.08422</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.20302</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.16698</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.24685</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.9936799999999999</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.75359</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.71012</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.5298099999999999</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.41214</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34314</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.10752</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.71799</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.7114</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.18039</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.6765099999999999</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.85073</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.53732</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.58205</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.19928</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.5879800000000001</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.5202899999999999</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.64934</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.5805499999999999</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.5210399999999999</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.5131599999999999</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.50659</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.39859</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.45442</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.40766</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.44188</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.50526</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.5180800000000001</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.57213</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.49107</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.49118</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.45648</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.48858</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.67587</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.93225</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.16651</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.30773</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.8369</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.55012</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.66552</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.9031699999999999</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.8633099999999999</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.16281</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.43937</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.77229</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.9517</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.20298</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.68823</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.12255</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.5220399999999999</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.48489</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.65354</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.9947999999999999</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.10146</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.24829</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.16709</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.05939</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.98029</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.02526</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.98921</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.24981</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.43949</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.79214</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.34709</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.19983</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.18931</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.84677</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.07265</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.15972</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.12097</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.15243</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.25332</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.31689</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.15247</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.26817</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.18698</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.18576</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.18599</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.18729</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.18747</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.17298</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.15056</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.17535</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.72305</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.5223300000000001</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.72521</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.3216</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.74333</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.49331</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40513</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.32358</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.47737</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.5042300000000001</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.52264</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.45503</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.42549</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.45437</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.7158600000000001</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.8470599999999999</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.61429</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.7010599999999999</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.72609</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.84462</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.70455</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.55026</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.54931</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.53804</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.59184</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.47019</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.08458</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.30108</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.28032</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.26769</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.54962</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.48174</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.51164</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.46616</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.6324500000000001</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.50176</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.48268</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.39921</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.48281</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.5936399999999999</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.40245</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.50507</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.50554</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40863</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.48574</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.40804</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40474</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34388</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.1897</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.96462</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.98048</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.58987</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.6444500000000001</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.5408500000000001</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.5253300000000001</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.5396799999999999</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.50822</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.50698</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.67804</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.52291</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.5232100000000001</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.50566</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.50651</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.50727</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.26831</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.07329000000000001</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.30592</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04285</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04377</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.04529</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.27254</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.08277</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.29145</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.12859</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04502</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.0471</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04677000000000001</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04595</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04668</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04634000000000001</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.25257</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.26819</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.27584</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.27905</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.42248</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.44579</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.5891900000000001</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.5345299999999999</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.38565</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.38931</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.5567300000000001</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.53637</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.5355800000000001</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3952</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33432</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.55322</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.45641</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.26967</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30447</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.30403</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.28512</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.29033</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26768</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.31391</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.38468</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.74063</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.87315</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.6738099999999999</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.64778</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.6667000000000001</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.7476699999999999</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.93816</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.48053</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.72921</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.73084</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.88676</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.62983</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.53525</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.48238</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.44873</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.08506999999999999</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29255</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.29893</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.72725</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.63805</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.60242</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.4806</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7885599999999999</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.78234</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.5999099999999999</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.7411599999999999</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.01748</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.40503</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.84229</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.43272</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.29551</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.78764</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.37949</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.04409</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.79935</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.39976</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.76431</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.44298</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.7737999999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80036</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78769</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78501</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87879</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50195</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41135</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46007</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21846</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63937</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54122</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.6128899999999999</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.58017</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.56014</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.56887</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.5755800000000001</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.50448</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.57713</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.55655</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.46587</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.48967</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.47717</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.5376599999999999</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.50928</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.51303</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.50959</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.5095299999999999</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.5456599999999999</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.5105299999999999</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.5627799999999999</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.46784</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.56547</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.4897</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43726</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.56362</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6662</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.07975</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.63815</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.50236</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.5689099999999999</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.59877</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.00104</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.33884</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.30643</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.27485</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.55916</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.8018</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.57284</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.65061</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.5502400000000001</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.95492</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.7760900000000001</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.72521</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.6417200000000001</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.57501</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.98754</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.92684</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.78549</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.5410199999999999</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.6692899999999999</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.58625</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.66806</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.62071</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.6613600000000001</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.7003400000000001</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.6383099999999999</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.65999</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.58202</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.57717</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.65795</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.6741200000000001</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.61942</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.66777</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.6864199999999999</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.7602300000000001</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.67701</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.75678</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.68631</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.68387</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.68551</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.66955</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.65907</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.6162300000000001</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.6582</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.60066</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.53873</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.6037100000000001</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.55161</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.57675</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.5531</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.5382400000000001</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.52777</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.46522</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9561000000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.57253</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.60305</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.61752</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.67555</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.53051</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.54449</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.49676</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.5208200000000001</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.4897</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.64073</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.40805</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.51219</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.61713</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.7267400000000001</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.8701</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.10983</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.93171</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.5443600000000001</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.11282</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.84257</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.94816</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.85812</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.63909</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.80867</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.06613</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.56611</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.52191</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.43195</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.37623</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.37457</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.87379</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.99037</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.5313099999999999</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.18867</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.7827200000000001</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.81229</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.7365700000000001</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.73885</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.40385</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.47501</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.3926</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.37604</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.44315</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37021</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39756</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.49945</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.4194</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.19594</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.51238</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70359</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79534</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64978</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5836399999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.7927000000000001</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.43542</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.74813</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.16498</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.9208</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.64247</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.6629</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.70009</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.55393</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.16342</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.61138</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.90865</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.57585</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.56916</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.33168</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.25624</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.22405</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.32992</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.0034</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.51802</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.60145</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.85841</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.50474</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.7496499999999999</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.07484</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.07275</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.9049700000000001</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.98222</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.93584</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.17345</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.15287</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.8613500000000001</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.15419</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.60661</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.96936</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.01464</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.15358</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.9491900000000001</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.9894299999999999</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.58362</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.92299</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.9803099999999999</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.08787</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.88439</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.87202</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.79244</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.09526</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.55328</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.9588099999999999</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.98985</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.7426200000000001</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.33148</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.6029099999999999</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.4864</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.48956</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.50339</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.44267</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.54688</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.39269</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.58501</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.49555</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.47627</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.48949</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.48535</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.52828</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.83302</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.7141000000000001</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.54328</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.5641900000000001</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.71841</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.8448</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.56636</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.57056</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.57233</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.5071100000000001</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.5068</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.55408</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.6127100000000001</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.55513</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.56626</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.45001</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.44612</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.4562</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.45857</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.6766599999999999</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.4027</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40542</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.53937</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.5073</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45648</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.5091</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.50242</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.50593</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.56737</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.44668</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.46725</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.56625</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.52407</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.53074</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.51775</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.5444500000000001</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.48848</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.51105</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.43787</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.39753</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.43655</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.39753</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.49751</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.5182</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.5242599999999999</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.5198700000000001</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.48181</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.46899</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.45212</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.55392</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.29347</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2815</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26674</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.46994</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.33378</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.48506</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.70101</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.6028300000000001</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.62774</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.8491000000000001</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.27164</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.16654</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.85229</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.42879</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.70147</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.9403400000000001</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.1681</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.12179</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.01868</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.5418999999999999</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.4388</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.42964</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39711</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49713</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44595</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.4132</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42488</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.5631</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.45869</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.43613</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.40141</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.4348399999999999</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.39796</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.43847</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.48149</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.5038899999999999</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.50439</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.57669</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.7115199999999999</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.0487</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.41359</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.10942</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.99073</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.97945</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.56605</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.54698</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.9464</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.08634</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.78395</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.01335</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.76795</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.64853</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.64126</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.70856</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.80015</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.29863</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.9500599999999999</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.53984</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.67272</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.33371</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.16032</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.62397</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.6576</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.67098</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.66604</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.64302</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.66751</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.20689</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.70044</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.78224</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.69775</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.70553</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.71368</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.63324</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.74798</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.02179</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.13159</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.69158</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.70003</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.6938</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.77342</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.72359</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.81298</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.66642</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.46298</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.06109</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.46331</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.57657</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.45354</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.48636</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34412</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.4479</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.5965199999999999</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.17287</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.4737</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.49673</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.39136</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.48725</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.46039</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.5046</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.4972200000000001</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.49212</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.43975</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39776</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40224</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.42533</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.7469</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49506</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.51064</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.51888</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28465</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.4065</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.45213</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.92218</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.47459</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.17946</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.90235</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.76327</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.45004</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39444</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.45568</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.50032</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.49748</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.44912</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.48987</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34929</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.40486</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.40482</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.43765</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.3693</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.44864</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.7465000000000001</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.42616</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.51502</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.68031</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.49588</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.40554</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.41863</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.42694</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.42187</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5661900000000001</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38969</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.42538</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.45378</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40094</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.66459</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.44921</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.45067</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43035</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65181</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.8316399999999999</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47209</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40275</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34479</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.5202599999999999</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.48531</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.48039</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.6948</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.46869</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.43904</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.4084</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.39616</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.43923</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.51647</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.41889</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.5461</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.7615599999999999</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.7682599999999999</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27723</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.47987</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.34218</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39417</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.54669</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.50164</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.7232799999999999</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.7627</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.5542999999999999</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.50188</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45117</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.02066</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.48744</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.44707</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.09503</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.12994</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.08394</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36809</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.11243</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.12889</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.01868</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.19447</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.14274</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.13196</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.17429</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.84137</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.19133</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.84846</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.34123</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.9039199999999999</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.73439</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.75783</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.9491000000000001</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.65707</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.38848</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.54427</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.53942</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.52837</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.53261</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.75593</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.37035</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.34539</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.42728</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.5144</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.6100599999999999</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.60448</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.52719</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.5095</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.5718300000000001</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.5876</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.58857</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.51428</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.5825199999999999</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.5291399999999999</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.5717000000000001</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.5029399999999999</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.46017</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.46778</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.46774</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.50102</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.42906</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.49807</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45687</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.6362899999999999</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.54672</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.49825</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.6795</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.5362100000000001</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.02412</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.77248</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.74042</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.27903</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.34054</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.71686</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.6404</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.34707</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.99438</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.59092</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.49281</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.49435</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.53886</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.5893400000000001</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.73265</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.17595</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.6903899999999999</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.9113600000000001</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.6640900000000001</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.93299</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.87949</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.74406</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.71332</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.17504</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.17622</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.42411</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.23513</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.61436</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.20289</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.2823</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.07564</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.3973</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.03281</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.66279</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.63406</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.43021</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.13436</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.6319</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.47261</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.50388</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45158</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40084</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.44887</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.48271</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40501</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.52522</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.5318200000000001</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.8008</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.6678099999999999</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.64896</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.50878</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.06728</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.66562</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.66323</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.7956599999999999</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.04757</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.1661</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.49943</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.192</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.54598</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.15305</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.55668</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.57174</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42789</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.49748</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.23461</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.37327</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.42977</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.47862</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.45915</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.50061</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.51129</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.46054</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41264</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43134</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.53812</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.51523</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.59672</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38445</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38194</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36413</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.75617</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.12709</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.68568</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.55013</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.45798</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.41196</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.39877</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.41656</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.41785</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.43161</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.38126</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.49272</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.4546</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.30411</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.44751</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37586</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.41196</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.44494</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.58021</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.47732</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.44792</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.39912</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.46197</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.44882</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.46306</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.5450499999999999</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44586</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.42311</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39762</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.41175</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.45958</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.41924</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.46756</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.49054</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.4746</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.4793</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.49728</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.45897</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.40536</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.38668</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.36864</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.36945</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.85838</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.39744</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.4807</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.40372</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.42099</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.44055</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.43421</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.42913</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.42882</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.38086</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.23333</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.30569</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.2667</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.38303</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.38238</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.29606</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.11005</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.6980599999999999</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.17184</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.25957</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.09684999999999999</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.35479</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.6879700000000001</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.5584199999999999</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.30076</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.30078</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.27347</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.49143</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.34283</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.49043</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.36377</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.39011</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.36541</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.39837</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.39814</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.38111</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.38374</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.41238</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.40641</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.39147</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38102</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42699</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.80191</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3825</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.46564</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39166</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38736</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.38748</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38406</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.48406</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.09277</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.36514</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.84173</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.80098</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.52152</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.75285</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.7514299999999999</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.51174</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41555</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.42679</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.42418</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.4063</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.41304</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.39325</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.38579</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44122</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.5539700000000001</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.42445</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.38683</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.44179</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.50719</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.73262</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42303</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.5694600000000001</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.79701</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.45253</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.40126</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.7527</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.40908</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.5224800000000001</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.28221</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.28557</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.21605</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.06032</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.9529299999999999</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.28303</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.6100399999999999</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.54415</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.38462</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.49102</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.5750599999999999</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.7493500000000001</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.54571</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.5408099999999999</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.39526</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.75229</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.75075</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.57475</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.44795</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.4915</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.98433</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.7589400000000001</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.61793</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.7499</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.17143</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.60042</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.72611</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.62354</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.23523</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.8723</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.8577899999999999</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.8793200000000001</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.89791</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.15192</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.6383</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.93047</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.6782699999999999</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.95543</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.61811</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.6362</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.73482</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.61859</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.79071</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.24298</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.03358</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.9945499999999999</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.0071</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.51312</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.33987</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.04762</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.40945</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.7536900000000001</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.38925</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34522</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.55668</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.80098</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.5495800000000001</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.7506499999999999</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.7524400000000001</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.55889</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.45841</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40698</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.42799</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.41899</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.38239</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.38294</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36807</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38272</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.42184</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.40474</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42646</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.6271</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5901000000000001</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.5561200000000001</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.53716</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.44778</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.47307</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.49437</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.55702</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.81136</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.15263</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.11861</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.03152</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.12133</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.72474</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.71949</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.04235</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.06073</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.66777</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.5555</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.5619700000000001</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.5493899999999999</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.4771</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.28176</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.4636</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.54622</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.55144</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.54087</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.65691</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.54105</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.04295</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.6537500000000001</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.5465</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.49687</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.49742</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.48044</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.49742</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.48023</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.49789</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.5746</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.55491</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.55841</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.49585</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.51151</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.38365</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.42222</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.49829</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.55824</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.65689</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.15145</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.0544</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.65813</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.57977</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.15024</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.86324</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.65738</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.13929</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.8119299999999999</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.49221</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.50951</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.49703</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.43889</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.53273</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39848</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34433</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.70394</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.57775</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.58428</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.71761</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.5468099999999999</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.45088</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.39667</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.41881</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.39493</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39179</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37899</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38721</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.62559</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.58312</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.4158</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.6291</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.00362</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.17323</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.92387</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.96028</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.0093</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.9502999999999999</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.91661</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.94648</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.9304199999999999</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.91373</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.9160499999999999</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.39835</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.66747</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.02141</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.6669700000000001</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.01834</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.12086</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.10272</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.69774</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.92073</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.84163</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.90852</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.54143</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.6658</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.68828</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.73668</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.78675</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.1963</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.07641</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.01591</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.32852</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.01157</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.11066</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.91501</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.75119</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.7504299999999999</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.8129299999999999</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.69117</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.69071</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.55589</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.6881499999999999</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.7239500000000001</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.6843400000000001</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36871</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.74641</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40227</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.38602</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.69445</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.4608</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.73241</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.51954</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.50524</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.43917</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.99322</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.8903</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.00666</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.89485</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.01447</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.9973</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.99749</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.15987</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.06669</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.08652</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.4221</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.6649400000000001</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.5944400000000001</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.7172000000000001</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.70436</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.02576</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.69694</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.74996</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.13427</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.22709</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.42761</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.19622</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.3582</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.98051</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.39613</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.3754</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.73898</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.64974</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.41724</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.41906</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.80725</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.75467</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.80169</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.55514</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37511</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.42258</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36716</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.75382</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.43937</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3989</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37251</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.4979</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37724</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.81108</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.31369</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.00409</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.9342200000000001</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.9604400000000001</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.03389</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.16255</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.06178</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.8644400000000001</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.6934900000000001</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.2222</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.20855</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.20919</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.15202</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.86775</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.70366</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.09741</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.10829</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.10832</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.13456</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.10603</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.52067</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.20133</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.63951</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.5774199999999999</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.15272</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.73094</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.66315</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.18535</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.8615900000000001</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.06605</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.03194</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.04901</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.03626</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.06928</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.12832</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.05076</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.06136</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.18429</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.16283</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.21599</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.20345</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.26549</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.16955</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.14236</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.12017</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.1008</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.12695</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.17667</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.19426</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.17484</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1.07591</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.6735800000000001</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.61422</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.5654199999999999</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.54808</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.44887</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37558</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.53044</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.31379</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.31098</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.06788</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.47906</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.51988</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.44175</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.43286</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.42966</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.43153</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.43969</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.43442</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.43651</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.4374</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.43351</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.4257</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.43202</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.42684</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.42048</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.41686</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.40314</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.41908</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37185</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.84836</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.42874</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.5662699999999999</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.6834199999999999</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.6990599999999999</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.6507200000000001</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.94097</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.7519600000000001</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.94633</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.15809</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.30582</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.44482</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.43296</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.45957</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.54514</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.25191</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.85123</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.61854</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.73337</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.70064</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.50288</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.84436</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.86607</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.21403</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.77318</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.57997</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.5804900000000001</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.62676</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.70711</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.58266</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.7348300000000001</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.60979</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.19949</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.17616</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.41116</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.17751</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.17842</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.18364</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>1.10309</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.07784</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.20746</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.10555</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.19186</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.05039</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>1.08196</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.20653</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.08189</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.54213</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.80733</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.8041200000000001</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.5640299999999999</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38092</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.21318</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.8491299999999999</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.84963</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.55913</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.55457</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.56255</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.51548</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.5539400000000001</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.5212</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.5012300000000001</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.45973</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45997</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38113</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43863</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.39907</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.4952</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.49921</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.5478</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.5203099999999999</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.52047</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.5576</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.17566</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.88302</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.49398</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.17051</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.50946</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.5694400000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.8441799999999999</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.7951699999999999</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.5969800000000001</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.85292</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.50088</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.5229400000000001</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.5436599999999999</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.17768</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.70101</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.55537</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.17366</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.54926</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.5504</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.5807899999999999</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.79963</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.5551</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.7991699999999999</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.84911</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.17426</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.7987000000000001</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.68357</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.05115</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.1749</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.17588</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.17722</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.17515</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.82424</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.73245</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.64498</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.67655</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.6845399999999999</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.7311</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.83485</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.8180599999999999</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.6152000000000001</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.80657</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.75628</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.13657</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.75046</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.6094700000000001</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.63607</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.63825</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.61718</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.61454</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.70341</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.6705</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.8134400000000001</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.70409</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.60814</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.51249</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38405</v>
       </c>
     </row>
   </sheetData>
